--- a/evaluation_forms/007_pitch_competition_scoring_form--evaluation_forms.xlsx
+++ b/evaluation_forms/007_pitch_competition_scoring_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pitch</t>
+          <t>pitch_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pitch</t>
+          <t>Pitch 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>Team 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>innovation</t>
+          <t>innovation_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>innovation</t>
+          <t>Innovation 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>business_model</t>
+          <t>business_model_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>business model</t>
+          <t>Business Model 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -802,7 +802,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -929,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>innovation_choices</t>
+          <t>innovation_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>innovation_choices</t>
+          <t>innovation_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>business_model_choices</t>
+          <t>business_model_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>business_model_choices</t>
+          <t>business_model_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
